--- a/data/trans_dic/P21D_6_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P21D_6_R-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,62</t>
+          <t>0,0; 0,75</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,0; 2,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,43</t>
+          <t>0,0; 1,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,6</t>
+          <t>0,14; 1,55</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,66</t>
+          <t>0,25; 2,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,16</t>
+          <t>0,9; 3,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,32</t>
+          <t>0,68; 2,23</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,4</t>
+          <t>0,0; 3,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,64</t>
+          <t>1,12; 3,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,61</t>
+          <t>0,87; 2,73</t>
         </is>
       </c>
     </row>
@@ -822,12 +822,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,69</t>
+          <t>0,18; 1,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,07</t>
+          <t>0,2; 1,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,68</t>
+          <t>0,82; 1,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,19</t>
+          <t>0,57; 1,18</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1776</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2082</t>
+          <t>0; 3101</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2766</t>
+          <t>0; 3343</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4673</t>
+          <t>0; 4735</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2541</t>
+          <t>0; 2498</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>519; 5748</t>
+          <t>493; 5579</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5238</t>
+          <t>0; 7205</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1165</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6024</t>
+          <t>0; 5966</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1062; 12107</t>
+          <t>1158; 12048</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2887; 10717</t>
+          <t>3042; 10934</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6212; 18431</t>
+          <t>5437; 17734</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 7507</t>
+          <t>0; 6925</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4135; 15152</t>
+          <t>4640; 15117</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4883; 16617</t>
+          <t>5521; 17399</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4140</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>588; 5387</t>
+          <t>589; 6026</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>591; 5777</t>
+          <t>590; 5791</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3734; 17363</t>
+          <t>3267; 17559</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12203; 25981</t>
+          <t>12654; 26341</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17883; 37681</t>
+          <t>18139; 37511</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_6_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P21D_6_R-Clase-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,75</t>
+          <t>0,0; 0,64</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,55</t>
+          <t>0,13; 1,42</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 2,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,65</t>
+          <t>0,36; 2,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,23</t>
+          <t>0,85; 3,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,23</t>
+          <t>0,67; 2,06</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,13</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,64</t>
+          <t>1,33; 3,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,73</t>
+          <t>0,9; 2,6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,89</t>
+          <t>0,17; 1,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,31</t>
+          <t>0,13; 1,36</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,08</t>
+          <t>0,25; 1,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,7</t>
+          <t>0,81; 1,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,18</t>
+          <t>0,62; 1,24</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>510</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>510</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3101</t>
+          <t>0; 2767</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3343</t>
+          <t>0; 3084</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>525</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>2037</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4735</t>
+          <t>0; 4890</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2498</t>
+          <t>0; 2924</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>493; 5579</t>
+          <t>523; 5602</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7205</t>
+          <t>0; 4983</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5966</t>
+          <t>0; 4985</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5964</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10801</t>
+          <t>11375</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1158; 12048</t>
+          <t>1831; 12815</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3042; 10934</t>
+          <t>3287; 11758</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5437; 17734</t>
+          <t>6003; 18480</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8948</t>
+          <t>9278</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10257</t>
+          <t>10546</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6925</t>
+          <t>0; 7388</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4640; 15117</t>
+          <t>5150; 15276</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5521; 17399</t>
+          <t>5881; 16983</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2339</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2339</t>
+          <t>2424</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>589; 6026</t>
+          <t>618; 6168</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>590; 5791</t>
+          <t>602; 6405</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>18261</t>
+          <t>19255</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26859</t>
+          <t>27887</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3267; 17559</t>
+          <t>3767; 16492</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12654; 26341</t>
+          <t>13315; 27506</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18139; 37511</t>
+          <t>19708; 39259</t>
         </is>
       </c>
     </row>
